--- a/Tableau_de_synthese_2025.xlsx
+++ b/Tableau_de_synthese_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\Desktop\cloud\Documents SIO1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edesmarets\Desktop\portefolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0832A43-A689-4E37-AF18-C64FAC3A15CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E954AC2B-E180-4745-8263-184C83A235D1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="11595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -86,9 +86,6 @@
 ▸Développer son projet professionnel</t>
   </si>
   <si>
-    <t>Centre de formation :</t>
-  </si>
-  <si>
     <t>▢ SISR</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
     <t xml:space="preserve">N° candidat : </t>
   </si>
   <si>
-    <t xml:space="preserve">NOM et prénom : </t>
-  </si>
-  <si>
     <t>Période (sous la forme du JJ/MM/AA au JJ/MM/AA)</t>
   </si>
   <si>
@@ -119,12 +113,6 @@
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio :</t>
-  </si>
-  <si>
-    <t>SESSION 2024</t>
-  </si>
-  <si>
     <t>Utilisation de PHP pour créer un formulaire et récupérer les données</t>
   </si>
   <si>
@@ -144,6 +132,18 @@
   </si>
   <si>
     <t>Installation et configuration de GLPI pour faire un inventaire automatique par GPO.</t>
+  </si>
+  <si>
+    <t>NOM et prénom : DESMARETS Enzo</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://github.com/EnzoDES/Portefolio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centre de formation : </t>
+  </si>
+  <si>
+    <t>SESSION 2026</t>
   </si>
 </sst>
 </file>
@@ -680,9 +680,48 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -705,45 +744,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -765,9 +765,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -805,9 +805,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -840,9 +840,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -875,9 +892,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1065,84 +1099,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="22"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="24"/>
-      <c r="H3" s="30"/>
+      <c r="A3" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="37"/>
+      <c r="H3" s="43"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="28"/>
+      <c r="A4" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="41"/>
       <c r="F4" s="14" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="21" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="43"/>
+      <c r="A5" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="39" t="s">
-        <v>22</v>
+      <c r="A6" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>20</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>0</v>
@@ -1164,8 +1198,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32"/>
-      <c r="B7" s="40"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="32"/>
       <c r="C7" s="8" t="s">
         <v>9</v>
       </c>
@@ -1221,16 +1255,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="35"/>
+      <c r="A8" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="27"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1269,7 +1303,7 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B9" s="10">
         <v>2024</v>
@@ -1277,7 +1311,7 @@
       <c r="C9" s="16"/>
       <c r="D9" s="17"/>
       <c r="E9" s="17" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F9" s="17"/>
       <c r="G9" s="17"/>
@@ -1320,14 +1354,14 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B10" s="10">
         <v>2024</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="17" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E10" s="17"/>
       <c r="F10" s="17"/>
@@ -1371,7 +1405,7 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B11" s="10">
         <v>2024</v>
@@ -1379,7 +1413,7 @@
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
       <c r="E11" s="17" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F11" s="17"/>
       <c r="G11" s="17"/>
@@ -1422,22 +1456,22 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B12" s="10">
         <v>2025</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="17" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F12" s="17"/>
       <c r="G12" s="17"/>
       <c r="H12" s="18" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -1477,19 +1511,19 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B13" s="10">
         <v>2025</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="17" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H13" s="18"/>
       <c r="I13"/>
@@ -1530,21 +1564,21 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B14" s="10">
         <v>2025</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="17" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H14" s="18"/>
       <c r="I14"/>
@@ -1719,16 +1753,16 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A18" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="38"/>
+      <c r="A18" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="30"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -2081,16 +2115,16 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A26" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="37"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="38"/>
+      <c r="A26" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="30"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2535,6 +2569,11 @@
     <row r="80" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2542,11 +2581,6 @@
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
